--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7042.69</v>
+        <v>6964.23</v>
       </c>
     </row>
     <row r="3">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1937.33</v>
+        <v>1943.71</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>66894.11</v>
+        <v>67239.58</v>
       </c>
     </row>
     <row r="5">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5604.13</v>
+        <v>5643.68</v>
       </c>
     </row>
     <row r="6">
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9673</v>
+        <v>9621.9</v>
       </c>
     </row>
     <row r="7">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5564.27</v>
+        <v>5534.88</v>
       </c>
     </row>
     <row r="8">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10120.58</v>
+        <v>10366.69</v>
       </c>
     </row>
     <row r="9">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6770.66</v>
+        <v>6975.97</v>
       </c>
     </row>
     <row r="10">
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>924.92</v>
+        <v>921.63</v>
       </c>
     </row>
     <row r="11">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7946.03</v>
+        <v>7917.74</v>
       </c>
     </row>
     <row r="12">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1083.4</v>
+        <v>1090.53</v>
       </c>
     </row>
     <row r="13">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>772.49</v>
+        <v>794.9299999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8616.43</v>
+        <v>8577.91</v>
       </c>
     </row>
     <row r="15">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37719.11</v>
+        <v>37477.46</v>
       </c>
     </row>
     <row r="16">
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>962.37</v>
+        <v>948.4400000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2870.85</v>
+        <v>2809.09</v>
       </c>
     </row>
     <row r="18">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14414.6</v>
+        <v>14079.19</v>
       </c>
     </row>
     <row r="19">
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4291.33</v>
+        <v>4178.33</v>
       </c>
     </row>
     <row r="20">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>780.08</v>
+        <v>759.53</v>
       </c>
     </row>
     <row r="21">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12212.25</v>
+        <v>11890.66</v>
       </c>
     </row>
     <row r="22">
@@ -1785,7 +1785,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11133.93</v>
+        <v>10840.73</v>
       </c>
     </row>
     <row r="23">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8349.790000000001</v>
+        <v>8452.549999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8349.790000000001</v>
+        <v>8452.549999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3455.28</v>
+        <v>3501.28</v>
       </c>
     </row>
     <row r="26">
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>790.21</v>
+        <v>791.85</v>
       </c>
     </row>
     <row r="27">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7580.96</v>
+        <v>7477.89</v>
       </c>
     </row>
     <row r="28">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7375.57</v>
+        <v>7458.06</v>
       </c>
     </row>
     <row r="29">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1667.14</v>
+        <v>1673.46</v>
       </c>
     </row>
     <row r="30">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3353.09</v>
+        <v>3384.95</v>
       </c>
     </row>
     <row r="31">
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15753.49</v>
+        <v>15870.85</v>
       </c>
     </row>
     <row r="32">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>34655.57</v>
+        <v>34913.75</v>
       </c>
     </row>
     <row r="33">
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1196.34</v>
+        <v>1216.57</v>
       </c>
     </row>
     <row r="34">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>798.48</v>
+        <v>787.51</v>
       </c>
     </row>
     <row r="35">
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>968.59</v>
+        <v>955.28</v>
       </c>
     </row>
     <row r="36">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2696.28</v>
+        <v>2679.56</v>
       </c>
     </row>
     <row r="37">
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8890.559999999999</v>
+        <v>9059.59</v>
       </c>
     </row>
     <row r="38">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3398.03</v>
+        <v>3462.63</v>
       </c>
     </row>
     <row r="39">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2806.44</v>
+        <v>2799.02</v>
       </c>
     </row>
     <row r="40">
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>37395.96</v>
+        <v>37772.07</v>
       </c>
     </row>
     <row r="41">
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>14503.82</v>
+        <v>14649.7</v>
       </c>
     </row>
     <row r="42">
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2407.28</v>
+        <v>2431.49</v>
       </c>
     </row>
     <row r="43">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>35342</v>
+        <v>35168.23</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1043-150-CM25</t>
+          <t>707426-77-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6964.23</v>
+        <v>1713.05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>951405-375-CM25</t>
+          <t>707426-141-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,10 +600,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -611,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -626,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1943.71</v>
+        <v>1356.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1079689-398-CM25</t>
+          <t>1043-150-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -647,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -657,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -672,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -687,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>67239.58</v>
+        <v>6964.23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>907-211-CM25</t>
+          <t>951405-375-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -708,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -718,14 +722,10 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
-        </is>
-      </c>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -733,12 +733,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -748,13 +748,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5643.68</v>
+        <v>1943.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2713-64-CM26</t>
+          <t>1079689-398-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,27 +764,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9621.9</v>
+        <v>67239.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2713-67-CM26</t>
+          <t>907-211-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5534.88</v>
+        <v>5643.68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2713-102-CM26</t>
+          <t>2713-64-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10366.69</v>
+        <v>9621.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>951405-17-CM26</t>
+          <t>2713-67-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -992,13 +992,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6975.97</v>
+        <v>5534.88</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233615-31-CM26</t>
+          <t>2713-102-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1053,13 +1053,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>921.63</v>
+        <v>10366.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233615-30-CM26</t>
+          <t>951405-17-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1114,13 +1114,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7917.74</v>
+        <v>6975.97</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1428-9-CM26</t>
+          <t>1233615-30-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1090.53</v>
+        <v>7917.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>707426-44-CM26</t>
+          <t>1233615-31-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>794.9299999999999</v>
+        <v>921.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2713-294-CM26</t>
+          <t>1428-9-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1297,13 +1297,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8577.91</v>
+        <v>1090.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1195-125-CM26</t>
+          <t>707426-44-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37477.46</v>
+        <v>794.9299999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1233615-408-CM26</t>
+          <t>2713-294-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,12 +1389,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1404,12 +1404,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1419,13 +1419,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>948.4400000000001</v>
+        <v>8577.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1005-20-CM26</t>
+          <t>1195-125-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1440,22 +1440,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2809.09</v>
+        <v>37477.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2713-370-CM26</t>
+          <t>1233615-408-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>14079.19</v>
+        <v>948.4400000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1233615-471-CM26</t>
+          <t>1005-20-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1557,27 +1557,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4178.33</v>
+        <v>2809.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1905-40-CM26</t>
+          <t>2713-370-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1618,12 +1618,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.002.027-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1663,13 +1663,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>759.53</v>
+        <v>14079.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079689-120-CM26</t>
+          <t>1905-40-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.002.027-5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>11890.66</v>
+        <v>759.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1233615-469-CM26</t>
+          <t>1233615-471-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1785,13 +1785,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10840.73</v>
+        <v>4178.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>854-56-CM26</t>
+          <t>1079689-120-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1846,13 +1846,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8452.549999999999</v>
+        <v>11890.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>854-57-CM26</t>
+          <t>1233615-469-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8452.549999999999</v>
+        <v>10840.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1005-25-CM26</t>
+          <t>854-56-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1928,22 +1928,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3501.28</v>
+        <v>8452.549999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>707426-66-CM26</t>
+          <t>854-57-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2029,13 +2029,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>791.85</v>
+        <v>8452.549999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2713-488-CM26</t>
+          <t>1005-25-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2045,27 +2045,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7477.89</v>
+        <v>3501.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2713-507-CM26</t>
+          <t>707426-66-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2151,13 +2151,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>7458.06</v>
+        <v>791.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>951405-152-CM26</t>
+          <t>2713-488-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1673.46</v>
+        <v>7477.89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2182-84-CM26</t>
+          <t>2713-507-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2233,22 +2233,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2273,13 +2273,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3384.95</v>
+        <v>7458.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4610-29-CM26</t>
+          <t>951405-152-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2304,12 +2304,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15870.85</v>
+        <v>1673.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4610-28-CM26</t>
+          <t>2182-84-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2355,22 +2355,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>34913.75</v>
+        <v>3384.95</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1003-88-CM26</t>
+          <t>4610-29-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2411,27 +2411,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>Quality Rubber S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2456,13 +2456,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1216.57</v>
+        <v>15870.85</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>951405-212-CM26</t>
+          <t>4610-28-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>Quality Rubber S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>787.51</v>
+        <v>34913.75</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2182-109-CM26</t>
+          <t>1003-88-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>955.28</v>
+        <v>1216.57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>707426-93-CM26</t>
+          <t>951405-212-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2639,13 +2639,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2679.56</v>
+        <v>787.51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>854-105-CM26</t>
+          <t>2182-109-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2660,22 +2660,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9059.59</v>
+        <v>955.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1079689-245-CM26</t>
+          <t>707426-93-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3462.63</v>
+        <v>2679.56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2713-678-CM26</t>
+          <t>854-105-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2799.02</v>
+        <v>9059.59</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4610-45-CM26</t>
+          <t>1079689-245-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2883,13 +2883,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>37772.07</v>
+        <v>3462.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4610-43-CM26</t>
+          <t>2713-678-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>14649.7</v>
+        <v>2799.02</v>
       </c>
     </row>
     <row r="42">
@@ -3011,7 +3011,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1195-403-CM26</t>
+          <t>4610-45-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3026,22 +3026,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>Quality Rubber S.A.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.097.502-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3066,6 +3066,128 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
+        <v>37772.07</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4610-43-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Quality Rubber S.A.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>14649.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1195-403-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>35168.23</v>
       </c>
     </row>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707426-77-CM25</t>
+          <t>4140-5-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1713.05</v>
+        <v>1206.68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>707426-141-CM25</t>
+          <t>707426-7-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.328.681-7</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1356.08</v>
+        <v>682.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1043-150-CM25</t>
+          <t>3791-104-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>COMERCIAL Y DISTRIBUIDORA ULAP LIMITADA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.173.807-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>6964.23</v>
+        <v>6028.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>951405-375-CM25</t>
+          <t>3791-155-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,25 +707,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -733,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA TD TODO EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.967.556-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -748,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1943.71</v>
+        <v>788.0700000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1079689-398-CM25</t>
+          <t>3797-85-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -764,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -779,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -794,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>67239.58</v>
+        <v>4624.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>907-211-CM25</t>
+          <t>1005-16-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -825,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -855,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -870,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5643.68</v>
+        <v>2209.92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2713-64-CM26</t>
+          <t>742-16-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -886,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -916,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -931,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9621.9</v>
+        <v>937.6900000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2713-67-CM26</t>
+          <t>1195-77-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -947,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -962,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -977,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -992,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5534.88</v>
+        <v>19096.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2713-102-CM26</t>
+          <t>3797-116-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1008,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1023,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1038,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1053,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10366.69</v>
+        <v>831.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>951405-17-CM26</t>
+          <t>749-9-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1069,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1084,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1099,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1114,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6975.97</v>
+        <v>726.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1233615-30-CM26</t>
+          <t>854-39-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1130,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1145,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1160,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1175,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7917.74</v>
+        <v>3031.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233615-31-CM26</t>
+          <t>854-38-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1191,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1206,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1221,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1236,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>921.63</v>
+        <v>3031.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1428-9-CM26</t>
+          <t>907-50-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1252,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1282,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1297,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1090.53</v>
+        <v>14015.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>707426-44-CM26</t>
+          <t>1403-3147-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1313,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1328,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1343,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1358,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>794.9299999999999</v>
+        <v>2180.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2713-294-CM26</t>
+          <t>3791-329-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1374,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1389,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1404,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1419,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8577.91</v>
+        <v>1210.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1195-125-CM26</t>
+          <t>930039-17-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1435,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1450,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1465,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1480,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>37477.46</v>
+        <v>2207.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233615-408-CM26</t>
+          <t>951405-119-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1496,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1511,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1526,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.962.756-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1541,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>948.4400000000001</v>
+        <v>2564.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1005-20-CM26</t>
+          <t>2713-354-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1557,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1602,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2809.09</v>
+        <v>6126.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2713-370-CM26</t>
+          <t>707426-77-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1618,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1633,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1648,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1663,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>14079.19</v>
+        <v>1713.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1905-40-CM26</t>
+          <t>1286987-39-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1679,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.002.027-5</t>
+          <t>65.797.310-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1724,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>759.53</v>
+        <v>909.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1233615-471-CM26</t>
+          <t>2713-416-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1740,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1755,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1770,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1785,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4178.33</v>
+        <v>15233.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1079689-120-CM26</t>
+          <t>1057062-130-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1801,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1816,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1846,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11890.66</v>
+        <v>4437.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1233615-469-CM26</t>
+          <t>2713-429-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1862,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1877,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1892,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1907,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10840.73</v>
+        <v>12549.74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>854-56-CM26</t>
+          <t>2713-434-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1923,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1938,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1953,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1968,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8452.549999999999</v>
+        <v>12855.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>854-57-CM26</t>
+          <t>1195-242-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1984,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1999,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2014,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2029,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8452.549999999999</v>
+        <v>35995.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1005-25-CM26</t>
+          <t>3431-92-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2045,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2075,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2090,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3501.28</v>
+        <v>1059.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>707426-66-CM26</t>
+          <t>3431-97-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2106,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2121,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2136,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2151,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>791.85</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2713-488-CM26</t>
+          <t>3431-101-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2167,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2182,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.101.085-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2197,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2212,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>7477.89</v>
+        <v>4025.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2713-507-CM26</t>
+          <t>1043-68-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2228,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2243,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2258,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2273,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>7458.06</v>
+        <v>21370.19</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>951405-152-CM26</t>
+          <t>1403-3869-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2289,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2304,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2319,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2334,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1673.46</v>
+        <v>2234.48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2182-84-CM26</t>
+          <t>854-215-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2350,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2380,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2395,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3384.95</v>
+        <v>4648.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4610-29-CM26</t>
+          <t>707426-118-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2411,12 +2415,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2426,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2441,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>FUEGOCLIMA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.190.725-3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2456,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15870.85</v>
+        <v>5332.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4610-28-CM26</t>
+          <t>5019-2085-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2472,12 +2476,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2487,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2502,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>RUBCES</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.266.920-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2517,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>34913.75</v>
+        <v>14176.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1003-88-CM26</t>
+          <t>2182-99-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2533,12 +2537,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2548,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2563,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2578,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1216.57</v>
+        <v>1211.51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>951405-212-CM26</t>
+          <t>854-234-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2594,12 +2598,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2609,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2624,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2639,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>787.51</v>
+        <v>2467.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2182-109-CM26</t>
+          <t>854-235-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2655,27 +2659,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2685,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2700,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>955.28</v>
+        <v>2467.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>707426-93-CM26</t>
+          <t>2713-599-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2716,12 +2720,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2731,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2746,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2761,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2679.56</v>
+        <v>3285.39</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>854-105-CM26</t>
+          <t>2713-598-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2777,27 +2781,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2807,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2822,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>9059.59</v>
+        <v>3139.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079689-245-CM26</t>
+          <t>2713-583-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2838,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2853,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2868,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2883,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3462.63</v>
+        <v>781.9299999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2713-678-CM26</t>
+          <t>2713-613-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2899,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2944,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2799.02</v>
+        <v>1781.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4610-44-CM26</t>
+          <t>1286987-69-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2960,27 +2964,27 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>65.797.310-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>Corporación Municipal de Deportes y Recreación Coyhaique</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2990,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3005,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2431.49</v>
+        <v>1045.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4610-45-CM26</t>
+          <t>2151-244-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3021,12 +3025,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3036,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.602.293-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL DE PTO CISNES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3051,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3066,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>37772.07</v>
+        <v>1211.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4610-43-CM26</t>
+          <t>4609-300-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3082,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3112,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>HQT</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.097.502-8</t>
+          <t>76.399.126-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3127,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14649.7</v>
+        <v>4274.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1195-403-CM26</t>
+          <t>5019-2105-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3143,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>65.224.300-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3173,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>RUBCES</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.266.920-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3188,7 +3192,4090 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
+        <v>1404.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4649-133-CM25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>30351.61</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4649-134-CM25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>10561.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>930039-43-CM25</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>1276.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1079689-237-CM25</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>902.61</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3431-123-CM25</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.101.085-0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>FUEGOCLIMA SPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>77.190.725-3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>1116.19</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1079689-261-CM25</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>13119.9</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>707426-141-CM25</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>1356.08</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1113146-45-CM25</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1977.16</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>749-44-CM25</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>746.73</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1195-465-CM25</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>10359.62</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2713-929-CM25</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>21769.32</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>951405-326-CM25</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>7218.56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>854-327-CM25</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>2227.31</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>854-326-CM25</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>2227.31</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1005-123-CM25</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>1424.07</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4609-487-CM25</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>HQT</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.399.126-1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>4483.36</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3797-708-CM25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>11285.25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1079689-348-CM25</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>3108.19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1043-150-CM25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>6964.23</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>951405-375-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>1943.71</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1079689-398-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>LUIS ALEXANDER</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>67239.58</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>907-211-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>5643.68</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2713-64-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>9621.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2713-67-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>5534.88</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2713-102-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>10366.69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>951405-17-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>6975.97</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1233615-30-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>7917.74</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1233615-31-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>921.63</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1428-9-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>60.701.004-8</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>1090.53</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>707426-44-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>794.9299999999999</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2713-294-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>8577.91</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1195-125-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>37477.46</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1233615-408-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>948.4400000000001</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1005-20-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>2809.09</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2713-370-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>14079.19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1079689-120-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>11890.66</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1233615-469-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>10840.73</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1233615-471-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>12.364.273-2</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>4178.33</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1905-40-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.002.027-5</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>759.53</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>854-56-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>8452.549999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>854-57-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>8452.549999999999</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1005-25-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>3501.28</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>707426-66-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>791.85</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2713-488-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>7477.89</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2713-507-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>7458.06</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>951405-152-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1673.46</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2182-84-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>3384.95</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4610-28-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Quality Rubber S.A.</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>34913.75</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4610-29-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Quality Rubber S.A.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>15870.85</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1003-88-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1216.57</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2182-109-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>955.28</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>951405-212-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>787.51</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>707426-93-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>2679.56</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>854-105-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>COMERCIAL COMPARO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>9059.59</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1079689-245-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>60.505.627-K</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS XI ZONA</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>3462.63</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2713-678-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>2799.02</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4610-43-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Quality Rubber S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>14649.7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4610-44-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Quality Rubber S.A.</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>2431.49</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4610-45-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Quality Rubber S.A.</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>76.097.502-8</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>37772.07</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1195-403-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.240.300-2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
         <v>35168.23</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>749-20-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>829.37</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>886182-219-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>COMERCIAL TREBOL LIMITADA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>77.601.801-5</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>1004.69</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>951405-286-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>14421.18</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2713-876-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>942.88</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>951405-306-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>1425.14</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2713-936-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1330.79</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2713-937-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>813.89</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>907-50-CM25</t>
+          <t>1403-3147-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.004.101-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14015.49</v>
+        <v>2180.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1403-3147-CM25</t>
+          <t>907-50-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.004.101-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2180.07</v>
+        <v>14015.49</v>
       </c>
     </row>
     <row r="16">
@@ -2588,7 +2588,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>854-234-CM25</t>
+          <t>854-235-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>854-235-CM25</t>
+          <t>854-234-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>930039-43-CM25</t>
+          <t>1079689-237-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1276.2</v>
+        <v>902.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1079689-237-CM25</t>
+          <t>930039-43-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>902.61</v>
+        <v>1276.2</v>
       </c>
     </row>
     <row r="50">
@@ -4385,7 +4385,11 @@
           <t>61.980.840-1</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Aysén</t>
@@ -4444,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4749,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4932,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5329,7 +5333,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1079689-120-CM26</t>
+          <t>1905-40-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5354,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.002.027-5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5369,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5384,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>11890.66</v>
+        <v>759.53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1233615-469-CM26</t>
+          <t>1233615-471-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5430,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>JAIME GONZALO URIBE HERMOSILLA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>12.364.273-2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5445,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>10840.73</v>
+        <v>4178.33</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1233615-471-CM26</t>
+          <t>1079689-120-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5476,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5491,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>JAIME GONZALO URIBE HERMOSILLA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>12.364.273-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5506,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4178.33</v>
+        <v>11890.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1905-40-CM26</t>
+          <t>1233615-469-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5537,12 +5541,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.002.027-5</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICAC</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5552,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5567,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>759.53</v>
+        <v>10840.73</v>
       </c>
     </row>
     <row r="85">
@@ -5969,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6101,7 +6105,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6162,7 +6166,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6244,7 +6248,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2182-109-CM26</t>
+          <t>951405-212-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6264,17 +6268,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6284,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6299,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>955.28</v>
+        <v>787.51</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>951405-212-CM26</t>
+          <t>2182-109-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6325,17 +6329,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6345,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6360,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>787.51</v>
+        <v>955.28</v>
       </c>
     </row>
     <row r="98">
@@ -6427,7 +6431,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>854-105-CM26</t>
+          <t>1079689-245-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6452,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6467,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6482,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>9059.59</v>
+        <v>3462.63</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1079689-245-CM26</t>
+          <t>854-105-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6513,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XI ZONA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6528,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.290.943-K</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6543,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>3462.63</v>
+        <v>9059.59</v>
       </c>
     </row>
     <row r="101">
@@ -6650,7 +6654,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6711,7 +6715,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6772,7 +6776,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6793,7 +6797,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1195-403-CM26</t>
+          <t>707426-107-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6808,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6818,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6833,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>FUEGOCLIMA SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.190.725-3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6848,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>35168.23</v>
+        <v>2592.48</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>749-20-CM26</t>
+          <t>1195-403-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6864,12 +6868,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6879,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6894,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6909,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>829.37</v>
+        <v>35168.23</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>886182-219-CM26</t>
+          <t>749-20-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6930,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6955,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>COMERCIAL TREBOL LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>77.601.801-5</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6970,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1004.69</v>
+        <v>829.37</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>951405-286-CM26</t>
+          <t>886182-219-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7001,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7016,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL TREBOL LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.601.801-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7031,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>14421.18</v>
+        <v>1004.69</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2713-876-CM26</t>
+          <t>951405-286-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7052,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7062,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7077,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7092,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>942.88</v>
+        <v>14421.18</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>951405-306-CM26</t>
+          <t>2713-876-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7113,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7123,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.980.840-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7138,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7153,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1425.14</v>
+        <v>942.88</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2713-936-CM26</t>
+          <t>951405-306-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7179,17 +7183,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.840-1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7199,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7214,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1330.79</v>
+        <v>1425.14</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2713-937-CM26</t>
+          <t>2713-936-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7235,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7260,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7275,7 +7279,251 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
+        <v>1330.79</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2713-937-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
         <v>813.89</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2713-971-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>69.240.100-K</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>15195.89</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1113146-29-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>86.887.200-4</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>2695.97</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>951405-338-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>61.980.840-1</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>SODIMAC S.A.</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>1955.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -623,7 +623,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1871,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2058,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2123,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2188,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2375,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2684,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2749,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3058,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3184,11 @@
           <t>76.399.126-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3432,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3802,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3867,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4054,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4119,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4245,11 @@
           <t>76.399.126-1</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4371,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4497,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4867,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4932,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5058,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5245,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5615,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5741,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5806,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6115,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6607,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7038,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7103,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7168,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7416,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7481,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7546,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1505,7 +1509,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2440,7 +2448,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3497,7 +3509,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5583,7 +5583,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1079689-120-CM26</t>
+          <t>1233615-469-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.505.627-K</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5623,32 +5623,28 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>96.792.430-K</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>11890.66</v>
+        <v>10840.73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1233615-469-CM26</t>
+          <t>1079689-120-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5673,12 +5669,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.505.627-K</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5688,22 +5684,26 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>10840.73</v>
+        <v>11890.66</v>
       </c>
     </row>
     <row r="85">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7696,6 +7696,67 @@
       </c>
       <c r="M116" s="2" t="n">
         <v>1955.26</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1426103-95-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>1208.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/aysen.xlsx
@@ -6965,7 +6965,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
